--- a/home-assignment-master/data/branch_config.xlsx
+++ b/home-assignment-master/data/branch_config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dkdk1\PycharmProjects\PythonProjectUmi\home-assignment-master\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B93802-9312-42DB-8710-2FFA6C7C717E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7555FB16-75A0-47F4-AF1D-FF75821F0140}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-348" yWindow="1512" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Branches" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>BranchID</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>Languages</t>
-  </si>
-  <si>
-    <t>400</t>
   </si>
   <si>
     <t>Tel Aviv Showroom</t>
@@ -592,143 +589,143 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2">
+        <v>400</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>18</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>20</v>
-      </c>
-      <c r="K2" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>24</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>29</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>31</v>
-      </c>
-      <c r="K3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s">
         <v>33</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>34</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>35</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>36</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>37</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>38</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>39</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>40</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>41</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>42</v>
-      </c>
-      <c r="K4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
         <v>45</v>
       </c>
-      <c r="C5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>46</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>47</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>48</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>49</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>50</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>51</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>52</v>
-      </c>
-      <c r="K5" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
